--- a/imports/Fraccion.xlsx
+++ b/imports/Fraccion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Limpieza\LIMPIEZA_APP\sop_lavado_app\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3E2774-19E6-4F2B-85EF-852926142C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAFCC495-DD2C-421E-844A-F9F7B8736EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{B8AE8316-DE00-4F18-9EBC-F49DAD0CC8B9}"/>
   </bookViews>
@@ -457,22 +457,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>

--- a/imports/Fraccion.xlsx
+++ b/imports/Fraccion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Limpieza\LIMPIEZA_APP\sop_lavado_app\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAFCC495-DD2C-421E-844A-F9F7B8736EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9D9639-85C2-4B63-A7EB-E5098CD8193E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{B8AE8316-DE00-4F18-9EBC-F49DAD0CC8B9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
   <si>
     <t>BD</t>
   </si>
@@ -239,6 +239,24 @@
   </si>
   <si>
     <t>Revisar que todos los objetos queden correctamente acomodados.</t>
+  </si>
+  <si>
+    <t>ACOMODAR</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>FR-TA-001</t>
+  </si>
+  <si>
+    <t>FR-AC-001</t>
+  </si>
+  <si>
+    <t>Lavar Trastes</t>
+  </si>
+  <si>
+    <t>Acomodar Trastes</t>
   </si>
 </sst>
 </file>
@@ -321,7 +339,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -373,37 +391,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -447,10 +439,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -830,7 +819,7 @@
       <c r="I1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="16"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -1119,12 +1108,25 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="A12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="I12" s="5" t="s">
         <v>45</v>
       </c>
@@ -1133,12 +1135,31 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="A13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="6">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="3"/>

--- a/imports/Fraccion.xlsx
+++ b/imports/Fraccion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Limpieza\LIMPIEZA_APP\sop_lavado_app\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9D9639-85C2-4B63-A7EB-E5098CD8193E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6BCB6C-1633-4532-81BE-9175AC6B870F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{B8AE8316-DE00-4F18-9EBC-F49DAD0CC8B9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="80">
   <si>
     <t>BD</t>
   </si>
@@ -257,6 +257,27 @@
   </si>
   <si>
     <t>Acomodar Trastes</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>MH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOP </t>
+  </si>
+  <si>
+    <t>FR-MS-001</t>
+  </si>
+  <si>
+    <t>Mop Seco</t>
+  </si>
+  <si>
+    <t>FR-MH-001</t>
+  </si>
+  <si>
+    <t>Mop Humedo</t>
   </si>
 </sst>
 </file>
@@ -395,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -441,6 +462,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1162,15 +1190,42 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="A14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="17"/>
+      <c r="I14" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="3"/>
+      <c r="A15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="I15" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="3"/>
